--- a/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -504,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -518,14 +519,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -535,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -573,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -629,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -646,62 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>25,59%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>31,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>46,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27,66%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33,46%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,91%</t>
+          <t>38,86%</t>
         </is>
       </c>
     </row>
@@ -714,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>19,29; 32,97</t>
+          <t>21,62; 37,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,83; 35,66</t>
+          <t>22,8; 39,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,7; 33,39</t>
+          <t>21,14; 38,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,52; 24,02</t>
+          <t>26,63; 43,73</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,73; 37,45</t>
+          <t>22,88; 40,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,63; 36,21</t>
+          <t>37,67; 55,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,58; 48,76</t>
+          <t>26,68; 38,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,87; 17,55</t>
+          <t>25,43; 36,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 32,41</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>22,36; 33,76</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28,26; 39,97</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>9,43; 18,43</t>
+          <t>33,14; 45,37</t>
         </is>
       </c>
     </row>
@@ -786,62 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>36,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>23,75%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>34,81%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>16,34%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -854,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,64; 32,17</t>
+          <t>18,86; 35,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,08; 27,11</t>
+          <t>15,99; 31,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,43; 47,56</t>
+          <t>37,22; 54,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 21,06</t>
+          <t>27,48; 45,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,6; 38,19</t>
+          <t>22,25; 38,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,29; 34,67</t>
+          <t>26,2; 40,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,37; 36,98</t>
+          <t>25,84; 38,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,99; 26,64</t>
+          <t>20,88; 32,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>21,17; 31,89</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19,06; 29,08</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>29,81; 39,86</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>12,04; 22,01</t>
+          <t>33,38; 44,39</t>
         </is>
       </c>
     </row>
@@ -926,62 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>45,28%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>29,57%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>40,79%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -994,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>31,03; 50,4</t>
+          <t>35,65; 56,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,06; 40,27</t>
+          <t>26,47; 44,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,38; 51,52</t>
+          <t>35,29; 55,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 20,98</t>
+          <t>39,81; 57,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35,19; 51,76</t>
+          <t>22,34; 39,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,3; 36,38</t>
+          <t>35,11; 54,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,12; 48,81</t>
+          <t>40,52; 54,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,01; 22,84</t>
+          <t>26,83; 38,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,07; 48,49</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>24,43; 35,83</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>34,09; 47,49</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>8,06; 19,28</t>
+          <t>38,16; 52,39</t>
         </is>
       </c>
     </row>
@@ -1066,62 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30,52%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>41,13%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -1134,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>29,24; 39,39</t>
+          <t>32,3; 44,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,55; 35,05</t>
+          <t>28,31; 40,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34,22; 45,0</t>
+          <t>39,44; 51,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,06; 14,44</t>
+          <t>31,8; 43,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,99; 37,78</t>
+          <t>28,02; 39,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,98; 37,24</t>
+          <t>40,69; 52,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>36,92; 48,11</t>
+          <t>33,44; 41,41</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 18,98</t>
+          <t>30,15; 38,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>30,05; 37,58</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>27,24; 34,24</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>37,57; 45,43</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>8,98; 15,11</t>
+          <t>41,93; 50,35</t>
         </is>
       </c>
     </row>
@@ -1206,62 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>43,18%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>43,42%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>14,57%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -1274,62 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>32,21; 46,62</t>
+          <t>34,31; 50,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>36,64; 50,53</t>
+          <t>42,56; 57,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36,72; 50,98</t>
+          <t>41,0; 56,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,25; 26,2</t>
+          <t>31,7; 46,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,67; 41,19</t>
+          <t>40,15; 55,22</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>35,9; 50,13</t>
+          <t>40,57; 55,79</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,34; 49,99</t>
+          <t>35,42; 46,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,01; 17,69</t>
+          <t>43,24; 54,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,01; 41,18</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38,22; 48,2</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>39,04; 48,48</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>10,84; 19,21</t>
+          <t>43,14; 53,31</t>
         </is>
       </c>
     </row>
@@ -1346,62 +1175,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>36,15%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>34,37%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>44,61%</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
+          <t>48,39%</t>
         </is>
       </c>
     </row>
@@ -1414,62 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>26,04; 42,92</t>
+          <t>28,88; 47,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,5; 40,31</t>
+          <t>21,82; 44,2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29,25; 50,23</t>
+          <t>35,14; 56,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,41; 25,11</t>
+          <t>27,11; 46,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,55; 41,85</t>
+          <t>32,76; 54,13</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,57; 48,5</t>
+          <t>40,08; 61,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,91; 59,34</t>
+          <t>30,74; 43,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,56; 20,17</t>
+          <t>30,72; 46,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,88; 40,33</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>27,73; 42,44</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>37,39; 51,63</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>8,95; 20,04</t>
+          <t>41,1; 56,7</t>
         </is>
       </c>
     </row>
@@ -1486,62 +1285,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>44,06%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,5%</t>
+          <t>44,54%</t>
         </is>
       </c>
     </row>
@@ -1554,62 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>29,93; 35,92</t>
+          <t>33,13; 39,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>28,22; 33,96</t>
+          <t>32,05; 38,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36,1; 42,24</t>
+          <t>40,48; 47,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,93; 16,58</t>
+          <t>35,36; 41,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>31,16; 36,58</t>
+          <t>33,53; 39,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,1; 36,21</t>
+          <t>41,75; 48,36</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,75; 43,54</t>
+          <t>35,49; 39,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,35; 16,14</t>
+          <t>33,69; 38,33</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>31,36; 35,57</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30,13; 34,11</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>37,44; 42,0</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,9; 15,35</t>
+          <t>42,18; 46,97</t>
         </is>
       </c>
     </row>
@@ -1622,18 +1391,1297 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>26700</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24654</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>21377</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>28954</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>25058</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>39812</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55654</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>49712</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>61190</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>19558; 33707</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>18310; 31751</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>15006; 27312</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>22118; 36317</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18335; 32192</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>32586; 47574</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>46305; 66716</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>40798; 59304</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>52189; 71446</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>20356</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>42090</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>25826</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>33964</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>46511</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>45130</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>76054</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>14610; 27370</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>13326; 26069</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>34413; 49981</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19481; 32411</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>19337; 33801</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>26981; 41989</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>38333; 56507</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>35544; 54887</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>65234; 86748</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>27182</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27238</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>25755</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43344</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30237</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>70526</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>51171</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>55992</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>21404; 34050</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>20654; 34593</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20123; 31818</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>36186; 51917</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>17254; 30656</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>23655; 36947</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>61154; 81852</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>41669; 60371</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>47469; 65172</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>68951</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>60604</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89056</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>66005</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>71901</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89635</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>134956</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>132506</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>178691</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>59033; 80663</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>50409; 71650</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>77970; 101176</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>56714; 77329</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>58777; 82892</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>77716; 101096</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>120745; 149538</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>116918; 148299</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>162985; 195687</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>40805</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>64475</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>59388</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>43766</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>60850</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61872</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84570</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>125325</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>121260</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>33282; 49068</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>55682; 74909</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>50155; 68506</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>35281; 52035</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>50953; 70076</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>52473; 72161</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>73788; 97141</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>111453; 139221</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>108580; 134158</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>25838</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>15435</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24217</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>23682</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>28546</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>33295</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>49521</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>43981</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>57512</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>19903; 33024</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>10603; 21477</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>18922; 30566</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>17759; 30376</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>21782; 35993</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>26050; 40240</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>41322; 58818</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>35355; 53108</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>48846; 67388</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>388</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>654</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>796</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>209832</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>211711</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>261882</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>231906</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>236114</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>288817</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>441738</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>447825</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>550699</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>191056; 228986</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>192023; 231685</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>240590; 282075</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>212143; 251037</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>217074; 258052</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>268123; 310550</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>417527; 470372</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>419992; 477832</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>521540; 580802</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,62; 37,25</t>
+          <t>22,01; 37,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 39,55</t>
+          <t>22,23; 39,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,14; 38,48</t>
+          <t>21,62; 40,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,63; 43,73</t>
+          <t>27,32; 45,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,88; 40,17</t>
+          <t>23,5; 39,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,67; 55,0</t>
+          <t>36,6; 55,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,68; 38,45</t>
+          <t>26,18; 37,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,43; 36,97</t>
+          <t>25,21; 37,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,14; 45,37</t>
+          <t>32,74; 45,67</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,86; 35,34</t>
+          <t>18,35; 34,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,99; 31,28</t>
+          <t>15,93; 30,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,22; 54,06</t>
+          <t>36,19; 54,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27,48; 45,73</t>
+          <t>28,53; 46,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,25; 38,89</t>
+          <t>22,21; 37,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,2; 40,78</t>
+          <t>25,79; 40,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,84; 38,1</t>
+          <t>25,75; 37,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,88; 32,24</t>
+          <t>21,68; 32,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,38; 44,39</t>
+          <t>33,25; 44,85</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>35,65; 56,72</t>
+          <t>34,48; 55,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,47; 44,33</t>
+          <t>26,83; 44,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>35,29; 55,8</t>
+          <t>34,52; 55,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,81; 57,11</t>
+          <t>39,55; 56,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>22,34; 39,69</t>
+          <t>21,75; 39,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,11; 54,84</t>
+          <t>35,65; 54,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,52; 54,23</t>
+          <t>40,0; 53,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 38,88</t>
+          <t>27,1; 39,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>38,16; 52,39</t>
+          <t>37,84; 52,36</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,3; 44,14</t>
+          <t>32,02; 43,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,31; 40,24</t>
+          <t>27,74; 40,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,44; 51,18</t>
+          <t>39,43; 51,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,8; 43,36</t>
+          <t>30,81; 42,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 39,52</t>
+          <t>28,91; 40,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,69; 52,94</t>
+          <t>41,13; 53,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,44; 41,41</t>
+          <t>33,17; 41,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,15; 38,24</t>
+          <t>30,56; 38,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,93; 50,35</t>
+          <t>41,39; 49,79</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,31; 50,58</t>
+          <t>34,3; 50,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,56; 57,26</t>
+          <t>42,11; 56,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,0; 56,0</t>
+          <t>41,24; 55,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,7; 46,76</t>
+          <t>31,4; 46,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,15; 55,22</t>
+          <t>40,51; 55,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,57; 55,79</t>
+          <t>40,98; 56,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,42; 46,63</t>
+          <t>35,36; 46,7</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,24; 54,02</t>
+          <t>43,09; 53,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,14; 53,31</t>
+          <t>43,47; 53,47</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,88; 47,92</t>
+          <t>28,9; 48,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,82; 44,2</t>
+          <t>21,72; 42,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35,14; 56,76</t>
+          <t>33,97; 57,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27,11; 46,37</t>
+          <t>26,52; 46,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,76; 54,13</t>
+          <t>32,73; 52,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,08; 61,92</t>
+          <t>40,72; 61,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30,74; 43,75</t>
+          <t>31,06; 43,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,72; 46,15</t>
+          <t>30,71; 45,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,1; 56,7</t>
+          <t>41,28; 55,47</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,13; 39,71</t>
+          <t>33,44; 39,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,05; 38,67</t>
+          <t>32,35; 38,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,48; 47,46</t>
+          <t>40,8; 47,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,36; 41,84</t>
+          <t>35,59; 41,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,53; 39,86</t>
+          <t>33,49; 39,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,75; 48,36</t>
+          <t>41,76; 48,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,49; 39,98</t>
+          <t>35,25; 39,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,69; 38,33</t>
+          <t>33,73; 38,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,18; 46,97</t>
+          <t>42,2; 46,66</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19558; 33707</t>
+          <t>19917; 34005</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18310; 31751</t>
+          <t>17845; 31860</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15006; 27312</t>
+          <t>15344; 28389</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22118; 36317</t>
+          <t>22684; 37381</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18335; 32192</t>
+          <t>18832; 31571</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32586; 47574</t>
+          <t>31653; 47963</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46305; 66716</t>
+          <t>45427; 65868</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40798; 59304</t>
+          <t>40446; 59821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>52189; 71446</t>
+          <t>51548; 71923</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14610; 27370</t>
+          <t>14215; 26526</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13326; 26069</t>
+          <t>13277; 25427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34413; 49981</t>
+          <t>33458; 50177</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19481; 32411</t>
+          <t>20220; 32652</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19337; 33801</t>
+          <t>19304; 32995</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26981; 41989</t>
+          <t>26554; 41692</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38333; 56507</t>
+          <t>38199; 56299</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35544; 54887</t>
+          <t>36902; 55295</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65234; 86748</t>
+          <t>64977; 87656</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>21404; 34050</t>
+          <t>20699; 33466</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20654; 34593</t>
+          <t>20939; 34643</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20123; 31818</t>
+          <t>19685; 31863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36186; 51917</t>
+          <t>35951; 51412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17254; 30656</t>
+          <t>16797; 30827</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23655; 36947</t>
+          <t>24018; 36784</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>61154; 81852</t>
+          <t>60371; 80145</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>41669; 60371</t>
+          <t>42082; 61215</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47469; 65172</t>
+          <t>47065; 65128</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59033; 80663</t>
+          <t>58517; 79656</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>50409; 71650</t>
+          <t>49399; 71335</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77970; 101176</t>
+          <t>77957; 100922</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56714; 77329</t>
+          <t>54938; 76020</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>58777; 82892</t>
+          <t>60643; 84047</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77716; 101096</t>
+          <t>78550; 102616</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120745; 149538</t>
+          <t>119779; 149484</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>116918; 148299</t>
+          <t>118513; 148529</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>162985; 195687</t>
+          <t>160884; 193510</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33282; 49068</t>
+          <t>33274; 49116</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55682; 74909</t>
+          <t>55095; 73984</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50155; 68506</t>
+          <t>50451; 68334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>35281; 52035</t>
+          <t>34950; 51985</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>50953; 70076</t>
+          <t>51419; 70229</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>52473; 72161</t>
+          <t>53003; 72837</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73788; 97141</t>
+          <t>73661; 97285</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111453; 139221</t>
+          <t>111062; 138953</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>108580; 134158</t>
+          <t>109395; 134558</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19903; 33024</t>
+          <t>19921; 33254</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10603; 21477</t>
+          <t>10552; 20749</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18922; 30566</t>
+          <t>18292; 30774</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17759; 30376</t>
+          <t>17376; 30356</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21782; 35993</t>
+          <t>21766; 35185</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26050; 40240</t>
+          <t>26462; 40054</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41322; 58818</t>
+          <t>41759; 58963</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35355; 53108</t>
+          <t>35342; 52486</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48846; 67388</t>
+          <t>49057; 65922</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>191056; 228986</t>
+          <t>192855; 230348</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>192023; 231685</t>
+          <t>193809; 230492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>240590; 282075</t>
+          <t>242468; 283645</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>212143; 251037</t>
+          <t>213551; 250660</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>217074; 258052</t>
+          <t>216825; 257732</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>268123; 310550</t>
+          <t>268158; 309009</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>417527; 470372</t>
+          <t>414787; 467484</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>419992; 477832</t>
+          <t>420491; 476872</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>521540; 580802</t>
+          <t>521762; 576991</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP25A_R-Clase-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34,87%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46,03%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>29,51%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>30,71%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>30,12%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>34,87%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>31,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,01; 37,58</t>
+          <t>27,33; 43,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,23; 39,68</t>
+          <t>23,7; 40,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21,62; 40,0</t>
+          <t>36,73; 54,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,32; 45,02</t>
+          <t>21,85; 37,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,5; 39,4</t>
+          <t>22,95; 39,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,6; 55,45</t>
+          <t>21,93; 41,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,18; 37,96</t>
+          <t>26,86; 37,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,21; 37,29</t>
+          <t>25,61; 37,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,74; 45,67</t>
+          <t>32,39; 45,43</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29,72%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32,98%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>26,28%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>23,16%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>45,52%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>36,9%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,72%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>32,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,35; 34,25</t>
+          <t>27,85; 47,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 30,51</t>
+          <t>22,36; 37,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,19; 54,27</t>
+          <t>26,2; 41,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28,53; 46,07</t>
+          <t>18,48; 34,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,21; 37,97</t>
+          <t>15,84; 32,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,79; 40,49</t>
+          <t>37,42; 53,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,75; 37,96</t>
+          <t>25,45; 37,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,68; 32,48</t>
+          <t>21,28; 32,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33,25; 44,85</t>
+          <t>33,2; 44,59</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47,68%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30,99%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>45,28%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>34,9%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>45,17%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>30,99%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>44,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>34,48; 55,74</t>
+          <t>39,38; 56,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 44,39</t>
+          <t>22,79; 40,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34,52; 55,88</t>
+          <t>34,62; 54,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,55; 56,56</t>
+          <t>35,21; 56,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,75; 39,91</t>
+          <t>26,93; 44,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>35,65; 54,6</t>
+          <t>35,23; 56,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,0; 53,1</t>
+          <t>40,29; 53,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,1; 39,42</t>
+          <t>26,96; 39,71</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>37,84; 52,36</t>
+          <t>37,69; 52,33</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34,28%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>46,93%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>37,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>34,03%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>45,05%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>37,01%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 43,59</t>
+          <t>31,28; 42,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>27,74; 40,06</t>
+          <t>28,75; 40,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,43; 51,05</t>
+          <t>40,94; 52,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,81; 42,63</t>
+          <t>32,48; 43,54</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,91; 40,07</t>
+          <t>28,25; 39,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,13; 53,73</t>
+          <t>39,4; 51,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 41,4</t>
+          <t>33,54; 41,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,56; 38,3</t>
+          <t>30,35; 38,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41,39; 49,79</t>
+          <t>42,28; 50,19</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>39,33%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>47,95%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>47,83%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>42,06%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>49,28%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>48,55%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>39,33%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,95%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>47,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,3; 50,63</t>
+          <t>32,34; 46,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,11; 56,55</t>
+          <t>40,42; 55,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,24; 55,86</t>
+          <t>41,16; 55,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31,4; 46,71</t>
+          <t>33,95; 49,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>40,51; 55,34</t>
+          <t>42,18; 56,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>40,98; 56,31</t>
+          <t>41,2; 55,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,36; 46,7</t>
+          <t>35,62; 46,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>43,09; 53,91</t>
+          <t>43,79; 54,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43,47; 53,47</t>
+          <t>42,79; 53,37</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>42,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>51,23%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>37,49%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>31,77%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>44,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36,15%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>42,93%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>51,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,9; 48,25</t>
+          <t>27,07; 46,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,72; 42,7</t>
+          <t>33,34; 52,71</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,97; 57,14</t>
+          <t>41,26; 61,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>26,52; 46,34</t>
+          <t>29,0; 47,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32,73; 52,92</t>
+          <t>21,63; 43,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,72; 61,63</t>
+          <t>34,5; 57,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,06; 43,86</t>
+          <t>30,02; 43,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,71; 45,61</t>
+          <t>31,42; 45,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>41,28; 55,47</t>
+          <t>40,73; 55,9</t>
         </is>
       </c>
     </row>
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38,65%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36,47%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>44,98%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>36,39%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>35,33%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>44,06%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>38,65%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>44,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>33,44; 39,95</t>
+          <t>35,61; 41,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>32,35; 38,47</t>
+          <t>33,31; 39,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,8; 47,73</t>
+          <t>41,95; 48,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35,59; 41,78</t>
+          <t>33,15; 39,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>33,49; 39,81</t>
+          <t>32,11; 38,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,76; 48,12</t>
+          <t>40,78; 47,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,25; 39,73</t>
+          <t>35,42; 39,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,73; 38,25</t>
+          <t>33,6; 38,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>42,2; 46,66</t>
+          <t>42,27; 46,8</t>
         </is>
       </c>
     </row>
@@ -1432,20 +1432,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión (tasa de respuesta: 99,49%)</t>
+          <t>Menores que emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión (tasa de respuesta: 99,49%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,32 +1533,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>28954</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25058</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>39812</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>26700</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>24654</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>21377</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28954</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>25058</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>39812</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>19917; 34005</t>
+          <t>22698; 36379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17845; 31860</t>
+          <t>18991; 32221</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15344; 28389</t>
+          <t>31765; 47198</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>22684; 37381</t>
+          <t>19775; 34312</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18832; 31571</t>
+          <t>18429; 31459</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31653; 47963</t>
+          <t>15564; 29213</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45427; 65868</t>
+          <t>46609; 65619</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40446; 59821</t>
+          <t>41081; 59917</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51548; 71923</t>
+          <t>51008; 71532</t>
         </is>
       </c>
     </row>
@@ -1696,32 +1696,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>25826</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>33964</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>20356</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>19304</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>42090</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26155</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>25826</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>33964</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14215; 26526</t>
+          <t>19739; 33413</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13277; 25427</t>
+          <t>19429; 32618</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33458; 50177</t>
+          <t>26975; 42371</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20220; 32652</t>
+          <t>14312; 26848</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19304; 32995</t>
+          <t>13201; 26749</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26554; 41692</t>
+          <t>34595; 49900</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38199; 56299</t>
+          <t>37746; 55993</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36902; 55295</t>
+          <t>36225; 55174</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64977; 87656</t>
+          <t>64884; 87152</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1912,32 +1912,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>43344</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23933</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>30237</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>27182</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>27238</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>25755</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>43344</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>23933</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>30237</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20699; 33466</t>
+          <t>35800; 51085</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20939; 34643</t>
+          <t>17600; 31010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19685; 31863</t>
+          <t>23324; 36994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35951; 51412</t>
+          <t>21135; 33806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16797; 30827</t>
+          <t>21018; 34428</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24018; 36784</t>
+          <t>20091; 32012</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60371; 80145</t>
+          <t>60807; 81159</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>42082; 61215</t>
+          <t>41867; 61657</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>47065; 65128</t>
+          <t>46881; 65098</t>
         </is>
       </c>
     </row>
@@ -2022,32 +2022,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>85</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>134</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>66005</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>71901</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89635</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>68951</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>60604</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>89056</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>66005</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>71901</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89635</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58517; 79656</t>
+          <t>55786; 75897</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49399; 71335</t>
+          <t>60312; 83905</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>77957; 100922</t>
+          <t>78183; 100673</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>54938; 76020</t>
+          <t>59347; 79558</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60643; 84047</t>
+          <t>50302; 71010</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>78550; 102616</t>
+          <t>77880; 101044</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119779; 149484</t>
+          <t>121088; 151569</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>118513; 148529</t>
+          <t>117722; 149627</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>160884; 193510</t>
+          <t>164316; 195054</t>
         </is>
       </c>
     </row>
@@ -2185,32 +2185,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2238,32 +2238,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>43766</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>60850</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>61872</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>40805</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>64475</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>59388</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>43766</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>60850</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>61872</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>33274; 49116</t>
+          <t>35993; 51968</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55095; 73984</t>
+          <t>51293; 70528</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>50451; 68334</t>
+          <t>53234; 71907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34950; 51985</t>
+          <t>32933; 48224</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>51419; 70229</t>
+          <t>55182; 74215</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>53003; 72837</t>
+          <t>50398; 68023</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>73661; 97285</t>
+          <t>74192; 96192</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>111062; 138953</t>
+          <t>112871; 139249</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>109395; 134558</t>
+          <t>107692; 134321</t>
         </is>
       </c>
     </row>
@@ -2348,32 +2348,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>34</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2401,32 +2401,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>23682</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28546</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>33295</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>25838</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>15435</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>24217</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>23682</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>28546</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>33295</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19921; 33254</t>
+          <t>17731; 30249</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>10552; 20749</t>
+          <t>22165; 35048</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18292; 30774</t>
+          <t>26815; 40112</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>17376; 30356</t>
+          <t>19987; 32815</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>21766; 35185</t>
+          <t>10511; 21120</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26462; 40054</t>
+          <t>18578; 30928</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41759; 58963</t>
+          <t>40357; 58992</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>35342; 52486</t>
+          <t>36159; 52703</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>49057; 65922</t>
+          <t>48406; 66431</t>
         </is>
       </c>
     </row>
@@ -2511,32 +2511,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>346</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>388</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>346</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>408</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>231906</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>236114</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>288817</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>209832</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>211711</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>261882</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>231906</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>236114</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>288817</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>192855; 230348</t>
+          <t>213629; 251045</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>193809; 230492</t>
+          <t>215679; 255255</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>242468; 283645</t>
+          <t>269358; 311293</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>213551; 250660</t>
+          <t>191170; 229141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>216825; 257732</t>
+          <t>192379; 232808</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>268158; 309009</t>
+          <t>242364; 282660</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>414787; 467484</t>
+          <t>416752; 469614</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>420491; 476872</t>
+          <t>418852; 476484</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>521762; 576991</t>
+          <t>522606; 578628</t>
         </is>
       </c>
     </row>
